--- a/src/Excelsior.Tests/BannerTests.ShiftsValidationsDown.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.ShiftsValidationsDown.verified.xlsx
@@ -111,7 +111,7 @@
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
 <columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
-  <sheet name="Employees">
+  <sheet name="Employees" bannerRows="1">
     <column index="1" property="Name"/>
     <column index="2" property="Age"/>
   </sheet>

--- a/src/Excelsior.Tests/BannerTests.ShiftsValidationsDown.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.ShiftsValidationsDown.verified.xlsx
@@ -63,7 +63,7 @@
     <col min="2" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Fill one row per employee.</t>

--- a/src/Excelsior.Tests/BannerTests.ShiftsValidationsDown.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.ShiftsValidationsDown.verified.xlsx
@@ -85,7 +85,7 @@
   </sheetData>
   <autoFilter ref="A2:B2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:XFD1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A7">
     <cfRule type="containsBlanks" dxfId="0" priority="1">

--- a/src/Excelsior.Tests/BannerTests.ShiftsValidationsDown.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.ShiftsValidationsDown.verified.xlsx
@@ -63,7 +63,7 @@
     <col min="2" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Fill one row per employee.</t>
@@ -85,7 +85,7 @@
   </sheetData>
   <autoFilter ref="A2:B2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:XFD1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A7">
     <cfRule type="containsBlanks" dxfId="0" priority="1">

--- a/src/Excelsior.Tests/BannerTests.ShiftsValidationsDown.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.ShiftsValidationsDown.verified.xlsx
@@ -111,7 +111,7 @@
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
 <columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
-  <sheet name="Employees" bannerRows="1">
+  <sheet name="Employees" banner="true">
     <column index="1" property="Name"/>
     <column index="2" property="Age"/>
   </sheet>

--- a/src/Excelsior.Tests/BannerTests.ShiftsValidationsDown.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.ShiftsValidationsDown.verified.xlsx
@@ -110,7 +110,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Employees" banner="true">
     <column index="1" property="Name"/>
     <column index="2" property="Age"/>
